--- a/artfynd/Bodsjön artfynd.xlsx
+++ b/artfynd/Bodsjön artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132415290</v>
+        <v>134956290</v>
       </c>
       <c r="B2" t="n">
-        <v>97235</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506303</v>
+        <v>506561</v>
       </c>
       <c r="R2" t="n">
-        <v>6922403</v>
+        <v>6922213</v>
       </c>
       <c r="S2" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johannes Esberg</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johannes Esberg</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104778203</v>
+        <v>134960254</v>
       </c>
       <c r="B3" t="n">
-        <v>80298</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,38 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506460</v>
+        <v>506544</v>
       </c>
       <c r="R3" t="n">
-        <v>6922640</v>
+        <v>6922137</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104779986</v>
+        <v>134963326</v>
       </c>
       <c r="B4" t="n">
-        <v>83173</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,38 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506624</v>
+        <v>506527</v>
       </c>
       <c r="R4" t="n">
-        <v>6922808</v>
+        <v>6922137</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,61 +954,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104778328</v>
+        <v>132415290</v>
       </c>
       <c r="B5" t="n">
-        <v>80433</v>
+        <v>97308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506488</v>
+        <v>506303</v>
       </c>
       <c r="R5" t="n">
-        <v>6922630</v>
+        <v>6922403</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,22 +1035,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,61 +1065,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johannes Esberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johannes Esberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104778682</v>
+        <v>134963948</v>
       </c>
       <c r="B6" t="n">
-        <v>83307</v>
+        <v>92199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506536</v>
+        <v>506525</v>
       </c>
       <c r="R6" t="n">
-        <v>6922750</v>
+        <v>6922125</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,22 +1142,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,22 +1162,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104779239</v>
+        <v>134955295</v>
       </c>
       <c r="B7" t="n">
-        <v>83307</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,38 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506535</v>
+        <v>506458</v>
       </c>
       <c r="R7" t="n">
-        <v>6922734</v>
+        <v>6922423</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,22 +1239,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,22 +1259,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104778301</v>
+        <v>134966130</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,20 +1300,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506488</v>
+        <v>506530</v>
       </c>
       <c r="R8" t="n">
-        <v>6922630</v>
+        <v>6922256</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,22 +1336,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,22 +1356,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104780368</v>
+        <v>134967191</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,20 +1397,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506561</v>
+        <v>506526</v>
       </c>
       <c r="R9" t="n">
-        <v>6922858</v>
+        <v>6922123</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,22 +1433,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,61 +1453,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104780537</v>
+        <v>134968052</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506561</v>
+        <v>506632</v>
       </c>
       <c r="R10" t="n">
-        <v>6922858</v>
+        <v>6922119</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,22 +1535,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,61 +1555,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104778294</v>
+        <v>134958299</v>
       </c>
       <c r="B11" t="n">
-        <v>80468</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506488</v>
+        <v>506492</v>
       </c>
       <c r="R11" t="n">
-        <v>6922630</v>
+        <v>6922305</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,22 +1636,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,22 +1656,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95289858</v>
+        <v>134958505</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,33 +1698,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ö Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506348</v>
+        <v>506548</v>
       </c>
       <c r="R12" t="n">
-        <v>6922836</v>
+        <v>6922129</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,22 +1737,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,22 +1757,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95295543</v>
+        <v>134959344</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,29 +1799,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ö messumyrvägen, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506498</v>
+        <v>506495</v>
       </c>
       <c r="R13" t="n">
-        <v>6922656</v>
+        <v>6922279</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1956,22 +1838,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,22 +1858,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95296324</v>
+        <v>134961332</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,33 +1900,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster messumyren, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506443</v>
+        <v>506526</v>
       </c>
       <c r="R14" t="n">
-        <v>6922815</v>
+        <v>6922254</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,22 +1939,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,61 +1959,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104778332</v>
+        <v>134962006</v>
       </c>
       <c r="B15" t="n">
-        <v>80392</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506488</v>
+        <v>506573</v>
       </c>
       <c r="R15" t="n">
-        <v>6922630</v>
+        <v>6922219</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,22 +2040,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,22 +2060,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95290818</v>
+        <v>134964153</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,29 +2102,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ö Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506360</v>
+        <v>506501</v>
       </c>
       <c r="R16" t="n">
-        <v>6922988</v>
+        <v>6922278</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2304,12 +2141,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,15 +2161,7549 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134964365</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>506571</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6922207</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134965295</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>506567</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6922217</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134966347</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>506513</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6922270</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134966766</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>506487</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6922297</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134971335</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>506532</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6922096</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134964367</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>506577</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6922196</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134966348</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>506590</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6922185</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134956490</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>506565</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6922247</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104778203</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80298</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>388</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>506460</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6922640</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134956362</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>506527</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6922779</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134958946</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>506567</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6922709</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134959747</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>506603</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6922913</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134960475</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506590</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6922803</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134958298</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506569</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6922696</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134969089</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>506560</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6922821</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>104779986</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>506624</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6922808</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>104778328</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>506488</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6922630</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134959139</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96410</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>506658</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6922763</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134966127</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92188</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>506531</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6922796</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134955725</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>506529</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6922807</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134960685</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>506606</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6922934</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134966559</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>506622</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6922760</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134970271</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>506481</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6922526</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>104778682</v>
+      </c>
+      <c r="B40" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>506536</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6922750</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>104779239</v>
+      </c>
+      <c r="B41" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>506535</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6922734</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>104778301</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>506488</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6922630</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>104780368</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>506561</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6922858</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134955509</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>506574</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6922792</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134956491</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>506564</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6922815</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134957888</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>506647</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6922836</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134958945</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>506566</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6922771</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134960481</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>506559</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6922721</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134960686</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>506613</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6922908</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134963947</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>506466</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6922520</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134965498</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>506644</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6922763</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134965499</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>506566</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6922652</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134966128</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>506464</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6922547</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134966345</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>506632</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6922858</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134966346</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>506483</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6922525</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134969464</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>506521</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6922762</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134971118</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>506534</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6922761</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>104780537</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>506561</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6922858</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134959538</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>506482</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6922524</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>104778294</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>506488</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6922630</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134971336</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>506615</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6922906</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134965500</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>506562</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6922744</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134966349</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>506683</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6922910</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>95289858</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ö Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>506348</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6922836</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>95295543</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ö messumyrvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>506498</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6922656</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>95296324</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Öster messumyren, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>506443</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6922815</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134956489</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>506524</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6922768</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134958729</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>506552</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6922723</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134959140</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>506658</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6922791</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134959537</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>506541</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6922735</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134964369</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>506480</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6922520</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134966765</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>506577</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6922786</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134970270</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>506521</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6922768</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134971119</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>506564</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6922773</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>104778332</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>506488</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6922630</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>134961123</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>658</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>506600</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6922972</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>134956911</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>506603</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6922972</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>134960480</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>506590</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6922951</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134960688</v>
+      </c>
+      <c r="B79" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>506594</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6922946</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134965091</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>506601</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6922972</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134968883</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>506607</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6922948</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>134964366</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>506618</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6922991</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134956912</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>506606</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6922997</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134958094</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>506624</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6923004</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134966557</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>506620</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6923009</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134962702</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>506624</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6923001</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134961330</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>506622</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6922999</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134957890</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>506623</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6922992</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>95290818</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ö Messumyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>506360</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6922988</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134965718</v>
+      </c>
+      <c r="B90" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>506620</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6923000</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>134968887</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bodsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>506624</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6922967</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Bodsjön artfynd.xlsx
+++ b/artfynd/Bodsjön artfynd.xlsx
@@ -1174,32 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134955295</v>
+        <v>134970271</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506458</v>
+        <v>506481</v>
       </c>
       <c r="R7" t="n">
-        <v>6922423</v>
+        <v>6922526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134966130</v>
+        <v>134955295</v>
       </c>
       <c r="B8" t="n">
         <v>80488</v>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506530</v>
+        <v>506458</v>
       </c>
       <c r="R8" t="n">
-        <v>6922256</v>
+        <v>6922423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134967191</v>
+        <v>134963947</v>
       </c>
       <c r="B9" t="n">
         <v>80488</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506526</v>
+        <v>506466</v>
       </c>
       <c r="R9" t="n">
-        <v>6922123</v>
+        <v>6922520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134968052</v>
+        <v>134966128</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,39 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506632</v>
+        <v>506464</v>
       </c>
       <c r="R10" t="n">
-        <v>6922119</v>
+        <v>6922547</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,49 +1562,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134958299</v>
+        <v>134966130</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506492</v>
+        <v>506530</v>
       </c>
       <c r="R11" t="n">
-        <v>6922305</v>
+        <v>6922256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,49 +1659,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134958505</v>
+        <v>134966346</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506548</v>
+        <v>506483</v>
       </c>
       <c r="R12" t="n">
-        <v>6922129</v>
+        <v>6922525</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,49 +1756,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134959344</v>
+        <v>134967191</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506495</v>
+        <v>506526</v>
       </c>
       <c r="R13" t="n">
-        <v>6922279</v>
+        <v>6922123</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,49 +1853,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134961332</v>
+        <v>134959538</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>80499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506526</v>
+        <v>506482</v>
       </c>
       <c r="R14" t="n">
-        <v>6922254</v>
+        <v>6922524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,37 +1950,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134962006</v>
+        <v>134968052</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2010,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506573</v>
+        <v>506632</v>
       </c>
       <c r="R15" t="n">
-        <v>6922219</v>
+        <v>6922119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,7 +2052,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134964153</v>
+        <v>134958299</v>
       </c>
       <c r="B16" t="n">
         <v>99195</v>
@@ -2102,7 +2082,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2111,10 +2091,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506501</v>
+        <v>506492</v>
       </c>
       <c r="R16" t="n">
-        <v>6922278</v>
+        <v>6922305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2153,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134964365</v>
+        <v>134958505</v>
       </c>
       <c r="B17" t="n">
         <v>99195</v>
@@ -2203,7 +2183,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2212,10 +2192,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506571</v>
+        <v>506548</v>
       </c>
       <c r="R17" t="n">
-        <v>6922207</v>
+        <v>6922129</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,7 +2254,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134965295</v>
+        <v>134959344</v>
       </c>
       <c r="B18" t="n">
         <v>99195</v>
@@ -2304,7 +2284,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2313,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506567</v>
+        <v>506495</v>
       </c>
       <c r="R18" t="n">
-        <v>6922217</v>
+        <v>6922279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,7 +2355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134966347</v>
+        <v>134961332</v>
       </c>
       <c r="B19" t="n">
         <v>99195</v>
@@ -2405,7 +2385,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2414,10 +2394,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506513</v>
+        <v>506526</v>
       </c>
       <c r="R19" t="n">
-        <v>6922270</v>
+        <v>6922254</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2456,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134966766</v>
+        <v>134962006</v>
       </c>
       <c r="B20" t="n">
         <v>99195</v>
@@ -2506,7 +2486,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2515,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506487</v>
+        <v>506573</v>
       </c>
       <c r="R20" t="n">
-        <v>6922297</v>
+        <v>6922219</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,7 +2557,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134971335</v>
+        <v>134964153</v>
       </c>
       <c r="B21" t="n">
         <v>99195</v>
@@ -2607,7 +2587,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2616,10 +2596,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506532</v>
+        <v>506501</v>
       </c>
       <c r="R21" t="n">
-        <v>6922096</v>
+        <v>6922278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,45 +2658,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134964367</v>
+        <v>134964365</v>
       </c>
       <c r="B22" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506577</v>
+        <v>506571</v>
       </c>
       <c r="R22" t="n">
-        <v>6922196</v>
+        <v>6922207</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,45 +2759,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134966348</v>
+        <v>134964369</v>
       </c>
       <c r="B23" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506590</v>
+        <v>506480</v>
       </c>
       <c r="R23" t="n">
-        <v>6922185</v>
+        <v>6922520</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2872,45 +2860,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134956490</v>
+        <v>134965295</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506565</v>
+        <v>506567</v>
       </c>
       <c r="R24" t="n">
-        <v>6922247</v>
+        <v>6922217</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2969,49 +2961,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104778203</v>
+        <v>134966347</v>
       </c>
       <c r="B25" t="n">
-        <v>80298</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506460</v>
+        <v>506513</v>
       </c>
       <c r="R25" t="n">
-        <v>6922640</v>
+        <v>6922270</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3035,22 +3030,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3065,57 +3050,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134956362</v>
+        <v>134966766</v>
       </c>
       <c r="B26" t="n">
-        <v>91974</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506527</v>
+        <v>506487</v>
       </c>
       <c r="R26" t="n">
-        <v>6922779</v>
+        <v>6922297</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,45 +3163,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134958946</v>
+        <v>134971335</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506567</v>
+        <v>506532</v>
       </c>
       <c r="R27" t="n">
-        <v>6922709</v>
+        <v>6922096</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,32 +3264,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134959747</v>
+        <v>134964367</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>98060</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3306,10 +3299,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506603</v>
+        <v>506577</v>
       </c>
       <c r="R28" t="n">
-        <v>6922913</v>
+        <v>6922196</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3368,32 +3361,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134960475</v>
+        <v>134966348</v>
       </c>
       <c r="B29" t="n">
-        <v>91974</v>
+        <v>98060</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3406,7 +3399,7 @@
         <v>506590</v>
       </c>
       <c r="R29" t="n">
-        <v>6922803</v>
+        <v>6922185</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,10 +3458,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134958298</v>
+        <v>134956490</v>
       </c>
       <c r="B30" t="n">
-        <v>92406</v>
+        <v>79131</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3476,21 +3469,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3500,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506569</v>
+        <v>506565</v>
       </c>
       <c r="R30" t="n">
-        <v>6922696</v>
+        <v>6922247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3562,10 +3555,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134969089</v>
+        <v>104778203</v>
       </c>
       <c r="B31" t="n">
-        <v>92406</v>
+        <v>80298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3573,37 +3566,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>388</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506560</v>
+        <v>506460</v>
       </c>
       <c r="R31" t="n">
-        <v>6922821</v>
+        <v>6922640</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3627,12 +3621,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3647,22 +3651,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104779986</v>
+        <v>134961123</v>
       </c>
       <c r="B32" t="n">
-        <v>83173</v>
+        <v>92245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3670,38 +3674,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506624</v>
+        <v>506600</v>
       </c>
       <c r="R32" t="n">
-        <v>6922808</v>
+        <v>6922972</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3725,22 +3728,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3755,22 +3748,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104778328</v>
+        <v>134956362</v>
       </c>
       <c r="B33" t="n">
-        <v>80433</v>
+        <v>91974</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3778,38 +3771,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506488</v>
+        <v>506527</v>
       </c>
       <c r="R33" t="n">
-        <v>6922630</v>
+        <v>6922779</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3833,22 +3825,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3863,44 +3845,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134959139</v>
+        <v>134956911</v>
       </c>
       <c r="B34" t="n">
-        <v>96410</v>
+        <v>91974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3910,10 +3892,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506658</v>
+        <v>506603</v>
       </c>
       <c r="R34" t="n">
-        <v>6922763</v>
+        <v>6922972</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3972,32 +3954,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134966127</v>
+        <v>134958946</v>
       </c>
       <c r="B35" t="n">
-        <v>92188</v>
+        <v>91974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3008</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4007,10 +3989,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506531</v>
+        <v>506567</v>
       </c>
       <c r="R35" t="n">
-        <v>6922796</v>
+        <v>6922709</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4069,32 +4051,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134955725</v>
+        <v>134959747</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>91974</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4104,10 +4086,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506529</v>
+        <v>506603</v>
       </c>
       <c r="R36" t="n">
-        <v>6922807</v>
+        <v>6922913</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,32 +4148,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134960685</v>
+        <v>134960475</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>91974</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4201,10 +4183,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506606</v>
+        <v>506590</v>
       </c>
       <c r="R37" t="n">
-        <v>6922934</v>
+        <v>6922803</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4263,32 +4245,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134966559</v>
+        <v>134960480</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>91974</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4298,10 +4280,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506622</v>
+        <v>506590</v>
       </c>
       <c r="R38" t="n">
-        <v>6922760</v>
+        <v>6922951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4360,32 +4342,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134970271</v>
+        <v>134958298</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>92406</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4395,10 +4377,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506481</v>
+        <v>506569</v>
       </c>
       <c r="R39" t="n">
-        <v>6922526</v>
+        <v>6922696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4457,10 +4439,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104778682</v>
+        <v>134960688</v>
       </c>
       <c r="B40" t="n">
-        <v>83307</v>
+        <v>92406</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4468,38 +4450,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506536</v>
+        <v>506594</v>
       </c>
       <c r="R40" t="n">
-        <v>6922750</v>
+        <v>6922946</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4523,22 +4504,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,22 +4524,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104779239</v>
+        <v>134965091</v>
       </c>
       <c r="B41" t="n">
-        <v>83307</v>
+        <v>92406</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4576,38 +4547,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506535</v>
+        <v>506601</v>
       </c>
       <c r="R41" t="n">
-        <v>6922734</v>
+        <v>6922972</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4631,22 +4601,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4661,22 +4621,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104778301</v>
+        <v>134968883</v>
       </c>
       <c r="B42" t="n">
-        <v>80432</v>
+        <v>92406</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4684,38 +4644,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506488</v>
+        <v>506607</v>
       </c>
       <c r="R42" t="n">
-        <v>6922630</v>
+        <v>6922948</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4739,22 +4698,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4769,22 +4718,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104780368</v>
+        <v>134969089</v>
       </c>
       <c r="B43" t="n">
-        <v>80432</v>
+        <v>92406</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4792,38 +4741,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506561</v>
+        <v>506560</v>
       </c>
       <c r="R43" t="n">
-        <v>6922858</v>
+        <v>6922821</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4847,22 +4795,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4877,22 +4815,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134955509</v>
+        <v>104779986</v>
       </c>
       <c r="B44" t="n">
-        <v>80488</v>
+        <v>83173</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4900,37 +4838,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506574</v>
+        <v>506624</v>
       </c>
       <c r="R44" t="n">
-        <v>6922792</v>
+        <v>6922808</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4954,12 +4893,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4974,22 +4923,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134956491</v>
+        <v>104778328</v>
       </c>
       <c r="B45" t="n">
-        <v>80488</v>
+        <v>80433</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4997,37 +4946,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506564</v>
+        <v>506488</v>
       </c>
       <c r="R45" t="n">
-        <v>6922815</v>
+        <v>6922630</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5051,12 +5001,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5071,44 +5031,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134957888</v>
+        <v>134959139</v>
       </c>
       <c r="B46" t="n">
-        <v>80488</v>
+        <v>96410</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2812</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5078,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506647</v>
+        <v>506658</v>
       </c>
       <c r="R46" t="n">
-        <v>6922836</v>
+        <v>6922763</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5180,32 +5140,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134958945</v>
+        <v>134966127</v>
       </c>
       <c r="B47" t="n">
-        <v>80488</v>
+        <v>92188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>3008</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5215,10 +5175,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506566</v>
+        <v>506531</v>
       </c>
       <c r="R47" t="n">
-        <v>6922771</v>
+        <v>6922796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5277,32 +5237,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134960481</v>
+        <v>134964366</v>
       </c>
       <c r="B48" t="n">
-        <v>80488</v>
+        <v>91937</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5312,10 +5272,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506559</v>
+        <v>506618</v>
       </c>
       <c r="R48" t="n">
-        <v>6922721</v>
+        <v>6922991</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5374,32 +5334,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134960686</v>
+        <v>134955725</v>
       </c>
       <c r="B49" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5409,10 +5369,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506613</v>
+        <v>506529</v>
       </c>
       <c r="R49" t="n">
-        <v>6922908</v>
+        <v>6922807</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5471,32 +5431,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134963947</v>
+        <v>134956912</v>
       </c>
       <c r="B50" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5506,10 +5466,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506466</v>
+        <v>506606</v>
       </c>
       <c r="R50" t="n">
-        <v>6922520</v>
+        <v>6922997</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5568,32 +5528,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134965498</v>
+        <v>134958094</v>
       </c>
       <c r="B51" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5603,10 +5563,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506644</v>
+        <v>506624</v>
       </c>
       <c r="R51" t="n">
-        <v>6922763</v>
+        <v>6923004</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5665,32 +5625,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134965499</v>
+        <v>134960685</v>
       </c>
       <c r="B52" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5700,10 +5660,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506566</v>
+        <v>506606</v>
       </c>
       <c r="R52" t="n">
-        <v>6922652</v>
+        <v>6922934</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5762,32 +5722,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134966128</v>
+        <v>134966557</v>
       </c>
       <c r="B53" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5797,10 +5757,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506464</v>
+        <v>506620</v>
       </c>
       <c r="R53" t="n">
-        <v>6922547</v>
+        <v>6923009</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5859,32 +5819,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134966345</v>
+        <v>134966559</v>
       </c>
       <c r="B54" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5894,10 +5854,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506632</v>
+        <v>506622</v>
       </c>
       <c r="R54" t="n">
-        <v>6922858</v>
+        <v>6922760</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5956,10 +5916,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134966346</v>
+        <v>104778682</v>
       </c>
       <c r="B55" t="n">
-        <v>80488</v>
+        <v>83307</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5967,37 +5927,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506483</v>
+        <v>506536</v>
       </c>
       <c r="R55" t="n">
-        <v>6922525</v>
+        <v>6922750</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6021,12 +5982,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6041,22 +6012,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134969464</v>
+        <v>104779239</v>
       </c>
       <c r="B56" t="n">
-        <v>80488</v>
+        <v>83307</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6064,37 +6035,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506521</v>
+        <v>506535</v>
       </c>
       <c r="R56" t="n">
-        <v>6922762</v>
+        <v>6922734</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6118,12 +6090,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6138,22 +6120,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134971118</v>
+        <v>104778301</v>
       </c>
       <c r="B57" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6179,19 +6161,20 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506534</v>
+        <v>506488</v>
       </c>
       <c r="R57" t="n">
-        <v>6922761</v>
+        <v>6922630</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6215,12 +6198,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6235,44 +6228,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104780537</v>
+        <v>104780368</v>
       </c>
       <c r="B58" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6355,32 +6348,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134959538</v>
+        <v>134955509</v>
       </c>
       <c r="B59" t="n">
-        <v>80499</v>
+        <v>80488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6390,10 +6383,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>506482</v>
+        <v>506574</v>
       </c>
       <c r="R59" t="n">
-        <v>6922524</v>
+        <v>6922792</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6452,49 +6445,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>104778294</v>
+        <v>134956491</v>
       </c>
       <c r="B60" t="n">
-        <v>80468</v>
+        <v>80488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>506488</v>
+        <v>506564</v>
       </c>
       <c r="R60" t="n">
-        <v>6922630</v>
+        <v>6922815</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6518,22 +6510,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6548,22 +6530,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134971336</v>
+        <v>134957888</v>
       </c>
       <c r="B61" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6571,39 +6553,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>506615</v>
+        <v>506647</v>
       </c>
       <c r="R61" t="n">
-        <v>6922906</v>
+        <v>6922836</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,10 +6639,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134965500</v>
+        <v>134958945</v>
       </c>
       <c r="B62" t="n">
-        <v>58136</v>
+        <v>80488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6673,21 +6650,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6674,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>506562</v>
+        <v>506566</v>
       </c>
       <c r="R62" t="n">
-        <v>6922744</v>
+        <v>6922771</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,10 +6736,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134966349</v>
+        <v>134960481</v>
       </c>
       <c r="B63" t="n">
-        <v>58136</v>
+        <v>80488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6770,39 +6747,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>506683</v>
+        <v>506559</v>
       </c>
       <c r="R63" t="n">
-        <v>6922910</v>
+        <v>6922721</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6861,63 +6833,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>95289858</v>
+        <v>134960686</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ö Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>506348</v>
+        <v>506613</v>
       </c>
       <c r="R64" t="n">
-        <v>6922836</v>
+        <v>6922908</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6941,22 +6898,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6971,71 +6918,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>95295543</v>
+        <v>134962702</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ö messumyrvägen, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>506498</v>
+        <v>506624</v>
       </c>
       <c r="R65" t="n">
-        <v>6922656</v>
+        <v>6923001</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7059,22 +6995,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7089,75 +7015,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>95296324</v>
+        <v>134965498</v>
       </c>
       <c r="B66" t="n">
-        <v>99118</v>
+        <v>80488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Öster messumyren, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506443</v>
+        <v>506644</v>
       </c>
       <c r="R66" t="n">
-        <v>6922815</v>
+        <v>6922763</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7181,22 +7092,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7211,61 +7112,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134956489</v>
+        <v>134965499</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506524</v>
+        <v>506566</v>
       </c>
       <c r="R67" t="n">
-        <v>6922768</v>
+        <v>6922652</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7324,49 +7221,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134958729</v>
+        <v>134966345</v>
       </c>
       <c r="B68" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506552</v>
+        <v>506632</v>
       </c>
       <c r="R68" t="n">
-        <v>6922723</v>
+        <v>6922858</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7425,49 +7318,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134959140</v>
+        <v>134969464</v>
       </c>
       <c r="B69" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506658</v>
+        <v>506521</v>
       </c>
       <c r="R69" t="n">
-        <v>6922791</v>
+        <v>6922762</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7526,49 +7415,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134959537</v>
+        <v>134971118</v>
       </c>
       <c r="B70" t="n">
-        <v>99195</v>
+        <v>80488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506541</v>
+        <v>506534</v>
       </c>
       <c r="R70" t="n">
-        <v>6922735</v>
+        <v>6922761</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7627,52 +7512,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134964369</v>
+        <v>104780537</v>
       </c>
       <c r="B71" t="n">
-        <v>99195</v>
+        <v>80461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506480</v>
+        <v>506561</v>
       </c>
       <c r="R71" t="n">
-        <v>6922520</v>
+        <v>6922858</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7696,12 +7578,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7716,61 +7608,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134966765</v>
+        <v>134961330</v>
       </c>
       <c r="B72" t="n">
-        <v>99195</v>
+        <v>80499</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506577</v>
+        <v>506622</v>
       </c>
       <c r="R72" t="n">
-        <v>6922786</v>
+        <v>6922999</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7829,52 +7717,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134970270</v>
+        <v>104778294</v>
       </c>
       <c r="B73" t="n">
-        <v>99195</v>
+        <v>80468</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506521</v>
+        <v>506488</v>
       </c>
       <c r="R73" t="n">
-        <v>6922768</v>
+        <v>6922630</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7898,12 +7783,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7918,49 +7813,50 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134971119</v>
+        <v>134957890</v>
       </c>
       <c r="B74" t="n">
-        <v>99195</v>
+        <v>57972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -7969,10 +7865,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506564</v>
+        <v>506623</v>
       </c>
       <c r="R74" t="n">
-        <v>6922773</v>
+        <v>6922992</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8031,49 +7927,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>104778332</v>
+        <v>134971336</v>
       </c>
       <c r="B75" t="n">
-        <v>80392</v>
+        <v>57975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506488</v>
+        <v>506615</v>
       </c>
       <c r="R75" t="n">
-        <v>6922630</v>
+        <v>6922906</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8097,22 +7997,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-11-22</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8127,22 +8017,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134961123</v>
+        <v>134965500</v>
       </c>
       <c r="B76" t="n">
-        <v>92245</v>
+        <v>58136</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8150,21 +8040,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8174,10 +8064,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506600</v>
+        <v>506562</v>
       </c>
       <c r="R76" t="n">
-        <v>6922972</v>
+        <v>6922744</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8236,10 +8126,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134956911</v>
+        <v>134966349</v>
       </c>
       <c r="B77" t="n">
-        <v>91974</v>
+        <v>58136</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8247,34 +8137,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506603</v>
+        <v>506683</v>
       </c>
       <c r="R77" t="n">
-        <v>6922972</v>
+        <v>6922910</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8333,48 +8228,63 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134960480</v>
+        <v>95289858</v>
       </c>
       <c r="B78" t="n">
-        <v>91974</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Ö Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506590</v>
+        <v>506348</v>
       </c>
       <c r="R78" t="n">
-        <v>6922951</v>
+        <v>6922836</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8398,12 +8308,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8418,60 +8338,71 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134960688</v>
+        <v>95290818</v>
       </c>
       <c r="B79" t="n">
-        <v>92406</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Ö Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506594</v>
+        <v>506360</v>
       </c>
       <c r="R79" t="n">
-        <v>6922946</v>
+        <v>6922988</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8495,12 +8426,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8515,60 +8446,71 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134965091</v>
+        <v>95295543</v>
       </c>
       <c r="B80" t="n">
-        <v>92406</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Ö messumyrvägen, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506601</v>
+        <v>506498</v>
       </c>
       <c r="R80" t="n">
-        <v>6922972</v>
+        <v>6922656</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8592,12 +8534,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8612,60 +8564,75 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134968883</v>
+        <v>95296324</v>
       </c>
       <c r="B81" t="n">
-        <v>92406</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Öster messumyren, Mpd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506607</v>
+        <v>506443</v>
       </c>
       <c r="R81" t="n">
-        <v>6922948</v>
+        <v>6922815</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8689,12 +8656,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2021-08-05</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8709,57 +8686,61 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134964366</v>
+        <v>134956489</v>
       </c>
       <c r="B82" t="n">
-        <v>91937</v>
+        <v>99195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506618</v>
+        <v>506524</v>
       </c>
       <c r="R82" t="n">
-        <v>6922991</v>
+        <v>6922768</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,10 +8799,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134956912</v>
+        <v>134958729</v>
       </c>
       <c r="B83" t="n">
-        <v>79373</v>
+        <v>99195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8829,34 +8810,38 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506606</v>
+        <v>506552</v>
       </c>
       <c r="R83" t="n">
-        <v>6922997</v>
+        <v>6922723</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8915,10 +8900,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134958094</v>
+        <v>134959140</v>
       </c>
       <c r="B84" t="n">
-        <v>79373</v>
+        <v>99195</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8926,34 +8911,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506624</v>
+        <v>506658</v>
       </c>
       <c r="R84" t="n">
-        <v>6923004</v>
+        <v>6922791</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9012,10 +9001,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134966557</v>
+        <v>134959537</v>
       </c>
       <c r="B85" t="n">
-        <v>79373</v>
+        <v>99195</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9023,34 +9012,38 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506620</v>
+        <v>506541</v>
       </c>
       <c r="R85" t="n">
-        <v>6923009</v>
+        <v>6922735</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9109,45 +9102,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134962702</v>
+        <v>134966765</v>
       </c>
       <c r="B86" t="n">
-        <v>80488</v>
+        <v>99195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>506624</v>
+        <v>506577</v>
       </c>
       <c r="R86" t="n">
-        <v>6923001</v>
+        <v>6922786</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9206,45 +9203,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134961330</v>
+        <v>134970270</v>
       </c>
       <c r="B87" t="n">
-        <v>80499</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>506622</v>
+        <v>506521</v>
       </c>
       <c r="R87" t="n">
-        <v>6922999</v>
+        <v>6922768</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9303,38 +9304,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134957890</v>
+        <v>134971119</v>
       </c>
       <c r="B88" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9343,10 +9343,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>506623</v>
+        <v>506564</v>
       </c>
       <c r="R88" t="n">
-        <v>6922992</v>
+        <v>6922773</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9405,59 +9405,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>95290818</v>
+        <v>134965718</v>
       </c>
       <c r="B89" t="n">
-        <v>99118</v>
+        <v>109924</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221184</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ö Messumyran, Mpd</t>
+          <t>Bodsjön, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>506360</v>
+        <v>506620</v>
       </c>
       <c r="R89" t="n">
-        <v>6922988</v>
+        <v>6923000</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9481,12 +9470,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9501,22 +9490,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134965718</v>
+        <v>134968887</v>
       </c>
       <c r="B90" t="n">
-        <v>109924</v>
+        <v>98060</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9524,21 +9513,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221184</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9548,10 +9537,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>506620</v>
+        <v>506624</v>
       </c>
       <c r="R90" t="n">
-        <v>6923000</v>
+        <v>6922967</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9610,10 +9599,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134968887</v>
+        <v>104778332</v>
       </c>
       <c r="B91" t="n">
-        <v>98060</v>
+        <v>80392</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9621,37 +9610,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bodsjön, Mpd</t>
+          <t>Messumyran, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>506624</v>
+        <v>506488</v>
       </c>
       <c r="R91" t="n">
-        <v>6922967</v>
+        <v>6922630</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9675,12 +9665,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9695,12 +9695,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
